--- a/Design/Excel/ET/Datas/__tables__.xlsx
+++ b/Design/Excel/ET/Datas/__tables__.xlsx
@@ -1250,406 +1250,369 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:K18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
-  <cols>
-    <col min="2" max="2" width="29.1083333333333" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="58.375" customWidth="1"/>
-    <col min="5" max="5" width="24.3333333333333" customWidth="1"/>
-    <col min="6" max="6" width="12.6666666666667" customWidth="1"/>
-    <col min="7" max="7" width="11.2166666666667" customWidth="1"/>
-    <col min="8" max="8" width="9.88333333333333" customWidth="1"/>
-    <col min="9" max="9" width="10.1083333333333" customWidth="1"/>
-    <col min="10" max="10" width="9.10833333333333" customWidth="1"/>
-    <col min="11" max="11" width="7.55" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" s="2" customFormat="1" spans="1:11">
-      <c r="B4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" s="2" customFormat="1" spans="1:11">
-      <c r="B5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" s="2" customFormat="1" spans="1:11">
-      <c r="B6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" s="2" customFormat="1" spans="1:11">
-      <c r="B7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" s="2" customFormat="1" spans="1:11">
-      <c r="B8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" s="2" customFormat="1" spans="1:11">
-      <c r="B9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" s="2" customFormat="1" spans="1:11">
-      <c r="B10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="B11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" t="s">
-        <v>50</v>
-      </c>
-      <c r="D11" t="b">
-        <v>1</v>
-      </c>
-      <c r="E11" t="s">
-        <v>51</v>
-      </c>
-      <c r="F11" t="s">
-        <v>52</v>
-      </c>
-      <c r="H11" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="B12" t="s">
-        <v>54</v>
-      </c>
-      <c r="C12" t="s">
-        <v>55</v>
-      </c>
-      <c r="D12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12" t="s">
-        <v>56</v>
-      </c>
-      <c r="F12" t="s">
-        <v>52</v>
-      </c>
-      <c r="H12" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="B13" t="s">
-        <v>57</v>
-      </c>
-      <c r="C13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" t="s">
-        <v>59</v>
-      </c>
-      <c r="F13" t="s">
-        <v>52</v>
-      </c>
-      <c r="H13" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="B14" t="s">
-        <v>60</v>
-      </c>
-      <c r="C14" t="s">
-        <v>61</v>
-      </c>
-      <c r="D14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E14" t="s">
-        <v>62</v>
-      </c>
-      <c r="F14" t="s">
-        <v>52</v>
-      </c>
-      <c r="H14" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="B15" t="s">
-        <v>63</v>
-      </c>
-      <c r="C15" t="s">
-        <v>64</v>
-      </c>
-      <c r="D15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="G15" t="s">
-        <v>66</v>
-      </c>
-      <c r="H15" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="B16" t="s">
-        <v>68</v>
-      </c>
-      <c r="C16" t="s">
-        <v>69</v>
-      </c>
-      <c r="D16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E16" t="s">
-        <v>70</v>
-      </c>
-      <c r="H16" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8">
-      <c r="B17" t="s">
-        <v>71</v>
-      </c>
-      <c r="C17" t="s">
-        <v>72</v>
-      </c>
-      <c r="D17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" t="s">
-        <v>73</v>
-      </c>
-      <c r="H17" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8">
-      <c r="B18" t="s">
-        <v>74</v>
-      </c>
-      <c r="C18" t="s">
-        <v>75</v>
-      </c>
-      <c r="D18" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" t="s">
-        <v>76</v>
-      </c>
-      <c r="H18" t="s">
-        <v>77</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="E15" r:id="rId1" display="OneConfig.xlsx"/>
-    <hyperlink ref="E7" r:id="rId2" display="Game/Sound@Sound.xlsx" tooltip="mailto:Sound@Sound.xlsx"/>
-    <hyperlink ref="E8" r:id="rId3" display="Game/UISound@Sound.xlsx"/>
-    <hyperlink ref="E9" r:id="rId1" display="Game/Music@Sound.xlsx"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
+<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <ns0:sheetPr/>
+  <ns0:dimension ref="A1:K18"/>
+  <ns0:sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <ns0:cols>
+    <ns0:col min="2" max="2" width="29.1083333333333" customWidth="1"/>
+    <ns0:col min="3" max="3" width="18" customWidth="1"/>
+    <ns0:col min="4" max="4" width="58.375" customWidth="1"/>
+    <ns0:col min="5" max="5" width="24.3333333333333" customWidth="1"/>
+    <ns0:col min="6" max="6" width="12.6666666666667" customWidth="1"/>
+    <ns0:col min="7" max="7" width="11.2166666666667" customWidth="1"/>
+    <ns0:col min="8" max="8" width="9.88333333333333" customWidth="1"/>
+    <ns0:col min="9" max="9" width="10.1083333333333" customWidth="1"/>
+    <ns0:col min="10" max="10" width="9.10833333333333" customWidth="1"/>
+    <ns0:col min="11" max="11" width="7.55" customWidth="1"/>
+  </ns0:cols>
+  <ns0:sheetData>
+    <ns0:row r="1" s="1" customFormat="1" spans="1:11">
+      <ns0:c r="A1" s="1" t="s">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
+      <ns0:c r="B1" s="1" t="s">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="C1" s="1" t="s">
+        <ns0:v>2</ns0:v>
+      </ns0:c>
+      <ns0:c r="D1" s="1" t="s">
+        <ns0:v>3</ns0:v>
+      </ns0:c>
+      <ns0:c r="E1" s="1" t="s">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
+      <ns0:c r="F1" s="1" t="s">
+        <ns0:v>5</ns0:v>
+      </ns0:c>
+      <ns0:c r="G1" s="1" t="s">
+        <ns0:v>6</ns0:v>
+      </ns0:c>
+      <ns0:c r="H1" s="1" t="s">
+        <ns0:v>7</ns0:v>
+      </ns0:c>
+      <ns0:c r="I1" s="1" t="s">
+        <ns0:v>8</ns0:v>
+      </ns0:c>
+      <ns0:c r="J1" s="1" t="s">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+      <ns0:c r="K1" s="1" t="s">
+        <ns0:v>10</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="2" s="1" customFormat="1" spans="1:11">
+      <ns0:c r="A2" s="1" t="s">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="B2" s="1" t="s">
+        <ns0:v>12</ns0:v>
+      </ns0:c>
+      <ns0:c r="C2" s="1" t="s">
+        <ns0:v>13</ns0:v>
+      </ns0:c>
+      <ns0:c r="D2" s="1" t="s">
+        <ns0:v>14</ns0:v>
+      </ns0:c>
+      <ns0:c r="E2" s="1" t="s">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="F2" s="1" t="s">
+        <ns0:v>16</ns0:v>
+      </ns0:c>
+      <ns0:c r="G2" s="1" t="s">
+        <ns0:v>17</ns0:v>
+      </ns0:c>
+      <ns0:c r="H2" s="1" t="s">
+        <ns0:v>18</ns0:v>
+      </ns0:c>
+      <ns0:c r="I2" s="1" t="s">
+        <ns0:v>19</ns0:v>
+      </ns0:c>
+      <ns0:c r="K2" s="1" t="s">
+        <ns0:v>20</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="3" s="1" customFormat="1" spans="1:11">
+      <ns0:c r="A3" s="1" t="s">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="D3" s="1" t="s">
+        <ns0:v>21</ns0:v>
+      </ns0:c>
+      <ns0:c r="E3" s="1" t="s">
+        <ns0:v>22</ns0:v>
+      </ns0:c>
+      <ns0:c r="F3" s="1" t="s">
+        <ns0:v>23</ns0:v>
+      </ns0:c>
+      <ns0:c r="G3" s="1" t="s">
+        <ns0:v>24</ns0:v>
+      </ns0:c>
+      <ns0:c r="H3" s="1" t="s">
+        <ns0:v>25</ns0:v>
+      </ns0:c>
+      <ns0:c r="K3" s="1" t="s">
+        <ns0:v>26</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="4" s="2" customFormat="1" spans="1:11">
+      <ns0:c r="B4" s="2" t="s">
+        <ns0:v>27</ns0:v>
+      </ns0:c>
+      <ns0:c r="C4" s="2" t="s">
+        <ns0:v>28</ns0:v>
+      </ns0:c>
+      <ns0:c r="D4" s="2" t="b">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="E4" s="2" t="s">
+        <ns0:v>29</ns0:v>
+      </ns0:c>
+      <ns0:c r="F4" s="2"/>
+      <ns0:c r="G4" s="2"/>
+      <ns0:c r="H4" s="2" t="s">
+        <ns0:v>30</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="5" s="2" customFormat="1" spans="1:11">
+      <ns0:c r="B5" s="2" t="s">
+        <ns0:v>31</ns0:v>
+      </ns0:c>
+      <ns0:c r="C5" s="2" t="s">
+        <ns0:v>32</ns0:v>
+      </ns0:c>
+      <ns0:c r="D5" s="2" t="b">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="E5" s="2" t="s">
+        <ns0:v>33</ns0:v>
+      </ns0:c>
+      <ns0:c r="F5" s="2"/>
+      <ns0:c r="G5" s="2"/>
+      <ns0:c r="H5" s="2" t="s">
+        <ns0:v>30</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="6" s="2" customFormat="1" spans="1:11">
+      <ns0:c r="B6" s="2" t="s">
+        <ns0:v>34</ns0:v>
+      </ns0:c>
+      <ns0:c r="C6" s="2" t="s">
+        <ns0:v>35</ns0:v>
+      </ns0:c>
+      <ns0:c r="D6" s="2" t="b">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="E6" s="2" t="s">
+        <ns0:v>36</ns0:v>
+      </ns0:c>
+      <ns0:c r="F6" s="3"/>
+      <ns0:c r="G6" s="2"/>
+      <ns0:c r="H6" s="2" t="s">
+        <ns0:v>30</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="7" s="2" customFormat="1" spans="1:11">
+      <ns0:c r="B7" s="2" t="s">
+        <ns0:v>37</ns0:v>
+      </ns0:c>
+      <ns0:c r="C7" s="2" t="s">
+        <ns0:v>38</ns0:v>
+      </ns0:c>
+      <ns0:c r="D7" s="2" t="b">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="E7" s="4" t="s">
+        <ns0:v>39</ns0:v>
+      </ns0:c>
+      <ns0:c r="F7" s="2"/>
+      <ns0:c r="G7" s="2"/>
+      <ns0:c r="H7" s="2" t="s">
+        <ns0:v>30</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="8" s="2" customFormat="1" spans="1:11">
+      <ns0:c r="B8" s="2" t="s">
+        <ns0:v>40</ns0:v>
+      </ns0:c>
+      <ns0:c r="C8" s="2" t="s">
+        <ns0:v>41</ns0:v>
+      </ns0:c>
+      <ns0:c r="D8" s="2" t="b">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="E8" s="4" t="s">
+        <ns0:v>42</ns0:v>
+      </ns0:c>
+      <ns0:c r="F8" s="2"/>
+      <ns0:c r="G8" s="2"/>
+      <ns0:c r="H8" s="2" t="s">
+        <ns0:v>30</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="9" s="2" customFormat="1" spans="1:11">
+      <ns0:c r="B9" s="2" t="s">
+        <ns0:v>43</ns0:v>
+      </ns0:c>
+      <ns0:c r="C9" s="2" t="s">
+        <ns0:v>44</ns0:v>
+      </ns0:c>
+      <ns0:c r="D9" s="2" t="b">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="E9" s="5" t="s">
+        <ns0:v>45</ns0:v>
+      </ns0:c>
+      <ns0:c r="F9" s="2"/>
+      <ns0:c r="G9" s="2"/>
+      <ns0:c r="H9" s="2" t="s">
+        <ns0:v>30</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="10" s="2" customFormat="1" spans="1:11">
+      <ns0:c r="B10" s="2" t="s">
+        <ns0:v>46</ns0:v>
+      </ns0:c>
+      <ns0:c r="C10" s="2" t="s">
+        <ns0:v>47</ns0:v>
+      </ns0:c>
+      <ns0:c r="D10" s="2" t="b">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="E10" s="2" t="s">
+        <ns0:v>48</ns0:v>
+      </ns0:c>
+      <ns0:c r="F10" s="2"/>
+      <ns0:c r="G10" s="2"/>
+      <ns0:c r="H10" s="2" t="s">
+        <ns0:v>30</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="11" spans="1:11">
+      <ns0:c r="B11" t="s">
+        <ns0:v>49</ns0:v>
+      </ns0:c>
+      <ns0:c r="C11" t="s">
+        <ns0:v>50</ns0:v>
+      </ns0:c>
+      <ns0:c r="D11" t="b">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="E11" t="s">
+        <ns0:v>51</ns0:v>
+      </ns0:c>
+      <ns0:c r="F11" t="s">
+        <ns0:v>52</ns0:v>
+      </ns0:c>
+      <ns0:c r="H11" t="s">
+        <ns0:v>53</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="12" spans="1:11">
+      <ns0:c r="B12" t="s">
+        <ns0:v>54</ns0:v>
+      </ns0:c>
+      <ns0:c r="C12" t="s">
+        <ns0:v>55</ns0:v>
+      </ns0:c>
+      <ns0:c r="D12" t="b">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="E12" t="s">
+        <ns0:v>56</ns0:v>
+      </ns0:c>
+      <ns0:c r="F12" t="s">
+        <ns0:v>52</ns0:v>
+      </ns0:c>
+      <ns0:c r="H12" t="s">
+        <ns0:v>53</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="13" spans="1:11">
+      <ns0:c r="B13" t="s">
+        <ns0:v>57</ns0:v>
+      </ns0:c>
+      <ns0:c r="C13" t="s">
+        <ns0:v>58</ns0:v>
+      </ns0:c>
+      <ns0:c r="D13" t="b">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="E13" t="s">
+        <ns0:v>59</ns0:v>
+      </ns0:c>
+      <ns0:c r="F13" t="s">
+        <ns0:v>52</ns0:v>
+      </ns0:c>
+      <ns0:c r="H13" t="s">
+        <ns0:v>53</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="14" spans="1:11">
+      <ns0:c r="B14" t="s">
+        <ns0:v>60</ns0:v>
+      </ns0:c>
+      <ns0:c r="C14" t="s">
+        <ns0:v>61</ns0:v>
+      </ns0:c>
+      <ns0:c r="D14" t="b">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="E14" t="s">
+        <ns0:v>62</ns0:v>
+      </ns0:c>
+      <ns0:c r="F14" t="s">
+        <ns0:v>52</ns0:v>
+      </ns0:c>
+      <ns0:c r="H14" t="s">
+        <ns0:v>53</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="16" spans="1:11">
+      <ns0:c r="B16" t="s">
+        <ns0:v>68</ns0:v>
+      </ns0:c>
+      <ns0:c r="C16" t="s">
+        <ns0:v>69</ns0:v>
+      </ns0:c>
+      <ns0:c r="D16" t="b">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="E16" t="s">
+        <ns0:v>70</ns0:v>
+      </ns0:c>
+      <ns0:c r="H16" t="s">
+        <ns0:v>67</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="17" spans="2:8">
+      <ns0:c r="B17" t="s">
+        <ns0:v>71</ns0:v>
+      </ns0:c>
+      <ns0:c r="C17" t="s">
+        <ns0:v>72</ns0:v>
+      </ns0:c>
+      <ns0:c r="D17" t="b">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="E17" t="s">
+        <ns0:v>73</ns0:v>
+      </ns0:c>
+      <ns0:c r="H17" t="s">
+        <ns0:v>67</ns0:v>
+      </ns0:c>
+    </ns0:row>
+  </ns0:sheetData>
+  <ns0:hyperlinks>
+    <ns0:hyperlink ref="E15" ns1:id="rId1" display="OneConfig.xlsx"/>
+    <ns0:hyperlink ref="E7" ns1:id="rId2" display="Game/Sound@Sound.xlsx" tooltip="mailto:Sound@Sound.xlsx"/>
+    <ns0:hyperlink ref="E8" ns1:id="rId3" display="Game/UISound@Sound.xlsx"/>
+    <ns0:hyperlink ref="E9" ns1:id="rId1" display="Game/Music@Sound.xlsx"/>
+  </ns0:hyperlinks>
+  <ns0:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ns0:pageSetup paperSize="9" orientation="portrait"/>
+  <ns0:headerFooter/>
+</ns0:worksheet>
 </file>
--- a/Design/Excel/ET/Datas/__tables__.xlsx
+++ b/Design/Excel/ET/Datas/__tables__.xlsx
@@ -1250,369 +1250,423 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <ns0:sheetPr/>
-  <ns0:dimension ref="A1:K18"/>
-  <ns0:sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
-  <ns0:cols>
-    <ns0:col min="2" max="2" width="29.1083333333333" customWidth="1"/>
-    <ns0:col min="3" max="3" width="18" customWidth="1"/>
-    <ns0:col min="4" max="4" width="58.375" customWidth="1"/>
-    <ns0:col min="5" max="5" width="24.3333333333333" customWidth="1"/>
-    <ns0:col min="6" max="6" width="12.6666666666667" customWidth="1"/>
-    <ns0:col min="7" max="7" width="11.2166666666667" customWidth="1"/>
-    <ns0:col min="8" max="8" width="9.88333333333333" customWidth="1"/>
-    <ns0:col min="9" max="9" width="10.1083333333333" customWidth="1"/>
-    <ns0:col min="10" max="10" width="9.10833333333333" customWidth="1"/>
-    <ns0:col min="11" max="11" width="7.55" customWidth="1"/>
-  </ns0:cols>
-  <ns0:sheetData>
-    <ns0:row r="1" s="1" customFormat="1" spans="1:11">
-      <ns0:c r="A1" s="1" t="s">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
-      <ns0:c r="B1" s="1" t="s">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-      <ns0:c r="C1" s="1" t="s">
-        <ns0:v>2</ns0:v>
-      </ns0:c>
-      <ns0:c r="D1" s="1" t="s">
-        <ns0:v>3</ns0:v>
-      </ns0:c>
-      <ns0:c r="E1" s="1" t="s">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
-      <ns0:c r="F1" s="1" t="s">
-        <ns0:v>5</ns0:v>
-      </ns0:c>
-      <ns0:c r="G1" s="1" t="s">
-        <ns0:v>6</ns0:v>
-      </ns0:c>
-      <ns0:c r="H1" s="1" t="s">
-        <ns0:v>7</ns0:v>
-      </ns0:c>
-      <ns0:c r="I1" s="1" t="s">
-        <ns0:v>8</ns0:v>
-      </ns0:c>
-      <ns0:c r="J1" s="1" t="s">
-        <ns0:v>9</ns0:v>
-      </ns0:c>
-      <ns0:c r="K1" s="1" t="s">
-        <ns0:v>10</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="2" s="1" customFormat="1" spans="1:11">
-      <ns0:c r="A2" s="1" t="s">
-        <ns0:v>11</ns0:v>
-      </ns0:c>
-      <ns0:c r="B2" s="1" t="s">
-        <ns0:v>12</ns0:v>
-      </ns0:c>
-      <ns0:c r="C2" s="1" t="s">
-        <ns0:v>13</ns0:v>
-      </ns0:c>
-      <ns0:c r="D2" s="1" t="s">
-        <ns0:v>14</ns0:v>
-      </ns0:c>
-      <ns0:c r="E2" s="1" t="s">
-        <ns0:v>15</ns0:v>
-      </ns0:c>
-      <ns0:c r="F2" s="1" t="s">
-        <ns0:v>16</ns0:v>
-      </ns0:c>
-      <ns0:c r="G2" s="1" t="s">
-        <ns0:v>17</ns0:v>
-      </ns0:c>
-      <ns0:c r="H2" s="1" t="s">
-        <ns0:v>18</ns0:v>
-      </ns0:c>
-      <ns0:c r="I2" s="1" t="s">
-        <ns0:v>19</ns0:v>
-      </ns0:c>
-      <ns0:c r="K2" s="1" t="s">
-        <ns0:v>20</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="3" s="1" customFormat="1" spans="1:11">
-      <ns0:c r="A3" s="1" t="s">
-        <ns0:v>11</ns0:v>
-      </ns0:c>
-      <ns0:c r="D3" s="1" t="s">
-        <ns0:v>21</ns0:v>
-      </ns0:c>
-      <ns0:c r="E3" s="1" t="s">
-        <ns0:v>22</ns0:v>
-      </ns0:c>
-      <ns0:c r="F3" s="1" t="s">
-        <ns0:v>23</ns0:v>
-      </ns0:c>
-      <ns0:c r="G3" s="1" t="s">
-        <ns0:v>24</ns0:v>
-      </ns0:c>
-      <ns0:c r="H3" s="1" t="s">
-        <ns0:v>25</ns0:v>
-      </ns0:c>
-      <ns0:c r="K3" s="1" t="s">
-        <ns0:v>26</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="4" s="2" customFormat="1" spans="1:11">
-      <ns0:c r="B4" s="2" t="s">
-        <ns0:v>27</ns0:v>
-      </ns0:c>
-      <ns0:c r="C4" s="2" t="s">
-        <ns0:v>28</ns0:v>
-      </ns0:c>
-      <ns0:c r="D4" s="2" t="b">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-      <ns0:c r="E4" s="2" t="s">
-        <ns0:v>29</ns0:v>
-      </ns0:c>
-      <ns0:c r="F4" s="2"/>
-      <ns0:c r="G4" s="2"/>
-      <ns0:c r="H4" s="2" t="s">
-        <ns0:v>30</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="5" s="2" customFormat="1" spans="1:11">
-      <ns0:c r="B5" s="2" t="s">
-        <ns0:v>31</ns0:v>
-      </ns0:c>
-      <ns0:c r="C5" s="2" t="s">
-        <ns0:v>32</ns0:v>
-      </ns0:c>
-      <ns0:c r="D5" s="2" t="b">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-      <ns0:c r="E5" s="2" t="s">
-        <ns0:v>33</ns0:v>
-      </ns0:c>
-      <ns0:c r="F5" s="2"/>
-      <ns0:c r="G5" s="2"/>
-      <ns0:c r="H5" s="2" t="s">
-        <ns0:v>30</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="6" s="2" customFormat="1" spans="1:11">
-      <ns0:c r="B6" s="2" t="s">
-        <ns0:v>34</ns0:v>
-      </ns0:c>
-      <ns0:c r="C6" s="2" t="s">
-        <ns0:v>35</ns0:v>
-      </ns0:c>
-      <ns0:c r="D6" s="2" t="b">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-      <ns0:c r="E6" s="2" t="s">
-        <ns0:v>36</ns0:v>
-      </ns0:c>
-      <ns0:c r="F6" s="3"/>
-      <ns0:c r="G6" s="2"/>
-      <ns0:c r="H6" s="2" t="s">
-        <ns0:v>30</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="7" s="2" customFormat="1" spans="1:11">
-      <ns0:c r="B7" s="2" t="s">
-        <ns0:v>37</ns0:v>
-      </ns0:c>
-      <ns0:c r="C7" s="2" t="s">
-        <ns0:v>38</ns0:v>
-      </ns0:c>
-      <ns0:c r="D7" s="2" t="b">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-      <ns0:c r="E7" s="4" t="s">
-        <ns0:v>39</ns0:v>
-      </ns0:c>
-      <ns0:c r="F7" s="2"/>
-      <ns0:c r="G7" s="2"/>
-      <ns0:c r="H7" s="2" t="s">
-        <ns0:v>30</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="8" s="2" customFormat="1" spans="1:11">
-      <ns0:c r="B8" s="2" t="s">
-        <ns0:v>40</ns0:v>
-      </ns0:c>
-      <ns0:c r="C8" s="2" t="s">
-        <ns0:v>41</ns0:v>
-      </ns0:c>
-      <ns0:c r="D8" s="2" t="b">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-      <ns0:c r="E8" s="4" t="s">
-        <ns0:v>42</ns0:v>
-      </ns0:c>
-      <ns0:c r="F8" s="2"/>
-      <ns0:c r="G8" s="2"/>
-      <ns0:c r="H8" s="2" t="s">
-        <ns0:v>30</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="9" s="2" customFormat="1" spans="1:11">
-      <ns0:c r="B9" s="2" t="s">
-        <ns0:v>43</ns0:v>
-      </ns0:c>
-      <ns0:c r="C9" s="2" t="s">
-        <ns0:v>44</ns0:v>
-      </ns0:c>
-      <ns0:c r="D9" s="2" t="b">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-      <ns0:c r="E9" s="5" t="s">
-        <ns0:v>45</ns0:v>
-      </ns0:c>
-      <ns0:c r="F9" s="2"/>
-      <ns0:c r="G9" s="2"/>
-      <ns0:c r="H9" s="2" t="s">
-        <ns0:v>30</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="10" s="2" customFormat="1" spans="1:11">
-      <ns0:c r="B10" s="2" t="s">
-        <ns0:v>46</ns0:v>
-      </ns0:c>
-      <ns0:c r="C10" s="2" t="s">
-        <ns0:v>47</ns0:v>
-      </ns0:c>
-      <ns0:c r="D10" s="2" t="b">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-      <ns0:c r="E10" s="2" t="s">
-        <ns0:v>48</ns0:v>
-      </ns0:c>
-      <ns0:c r="F10" s="2"/>
-      <ns0:c r="G10" s="2"/>
-      <ns0:c r="H10" s="2" t="s">
-        <ns0:v>30</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="11" spans="1:11">
-      <ns0:c r="B11" t="s">
-        <ns0:v>49</ns0:v>
-      </ns0:c>
-      <ns0:c r="C11" t="s">
-        <ns0:v>50</ns0:v>
-      </ns0:c>
-      <ns0:c r="D11" t="b">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-      <ns0:c r="E11" t="s">
-        <ns0:v>51</ns0:v>
-      </ns0:c>
-      <ns0:c r="F11" t="s">
-        <ns0:v>52</ns0:v>
-      </ns0:c>
-      <ns0:c r="H11" t="s">
-        <ns0:v>53</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="12" spans="1:11">
-      <ns0:c r="B12" t="s">
-        <ns0:v>54</ns0:v>
-      </ns0:c>
-      <ns0:c r="C12" t="s">
-        <ns0:v>55</ns0:v>
-      </ns0:c>
-      <ns0:c r="D12" t="b">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-      <ns0:c r="E12" t="s">
-        <ns0:v>56</ns0:v>
-      </ns0:c>
-      <ns0:c r="F12" t="s">
-        <ns0:v>52</ns0:v>
-      </ns0:c>
-      <ns0:c r="H12" t="s">
-        <ns0:v>53</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="13" spans="1:11">
-      <ns0:c r="B13" t="s">
-        <ns0:v>57</ns0:v>
-      </ns0:c>
-      <ns0:c r="C13" t="s">
-        <ns0:v>58</ns0:v>
-      </ns0:c>
-      <ns0:c r="D13" t="b">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-      <ns0:c r="E13" t="s">
-        <ns0:v>59</ns0:v>
-      </ns0:c>
-      <ns0:c r="F13" t="s">
-        <ns0:v>52</ns0:v>
-      </ns0:c>
-      <ns0:c r="H13" t="s">
-        <ns0:v>53</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="14" spans="1:11">
-      <ns0:c r="B14" t="s">
-        <ns0:v>60</ns0:v>
-      </ns0:c>
-      <ns0:c r="C14" t="s">
-        <ns0:v>61</ns0:v>
-      </ns0:c>
-      <ns0:c r="D14" t="b">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-      <ns0:c r="E14" t="s">
-        <ns0:v>62</ns0:v>
-      </ns0:c>
-      <ns0:c r="F14" t="s">
-        <ns0:v>52</ns0:v>
-      </ns0:c>
-      <ns0:c r="H14" t="s">
-        <ns0:v>53</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="16" spans="1:11">
-      <ns0:c r="B16" t="s">
-        <ns0:v>68</ns0:v>
-      </ns0:c>
-      <ns0:c r="C16" t="s">
-        <ns0:v>69</ns0:v>
-      </ns0:c>
-      <ns0:c r="D16" t="b">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-      <ns0:c r="E16" t="s">
-        <ns0:v>70</ns0:v>
-      </ns0:c>
-      <ns0:c r="H16" t="s">
-        <ns0:v>67</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="17" spans="2:8">
-      <ns0:c r="B17" t="s">
-        <ns0:v>71</ns0:v>
-      </ns0:c>
-      <ns0:c r="C17" t="s">
-        <ns0:v>72</ns0:v>
-      </ns0:c>
-      <ns0:c r="D17" t="b">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-      <ns0:c r="E17" t="s">
-        <ns0:v>73</ns0:v>
-      </ns0:c>
-      <ns0:c r="H17" t="s">
-        <ns0:v>67</ns0:v>
-      </ns0:c>
-    </ns0:row>
-  </ns0:sheetData>
-  <ns0:hyperlinks>
-    <ns0:hyperlink ref="E15" ns1:id="rId1" display="OneConfig.xlsx"/>
-    <ns0:hyperlink ref="E7" ns1:id="rId2" display="Game/Sound@Sound.xlsx" tooltip="mailto:Sound@Sound.xlsx"/>
-    <ns0:hyperlink ref="E8" ns1:id="rId3" display="Game/UISound@Sound.xlsx"/>
-    <ns0:hyperlink ref="E9" ns1:id="rId1" display="Game/Music@Sound.xlsx"/>
-  </ns0:hyperlinks>
-  <ns0:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ns0:pageSetup paperSize="9" orientation="portrait"/>
-  <ns0:headerFooter/>
-</ns0:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr/>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <cols>
+    <col min="2" max="2" width="29.1083333333333" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="58.375" customWidth="1"/>
+    <col min="5" max="5" width="24.3333333333333" customWidth="1"/>
+    <col min="6" max="6" width="12.6666666666667" customWidth="1"/>
+    <col min="7" max="7" width="11.2166666666667" customWidth="1"/>
+    <col min="8" max="8" width="9.88333333333333" customWidth="1"/>
+    <col min="9" max="9" width="10.1083333333333" customWidth="1"/>
+    <col min="10" max="10" width="9.10833333333333" customWidth="1"/>
+    <col min="11" max="11" width="7.55" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:11">
+      <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:11">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" s="2" customFormat="1" spans="1:11">
+      <c r="B4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" s="2" customFormat="1" spans="1:11">
+      <c r="B5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" spans="1:11">
+      <c r="B6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="3"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" s="2" customFormat="1" spans="1:11">
+      <c r="B7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" s="2" customFormat="1" spans="1:11">
+      <c r="B8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" s="2" customFormat="1" spans="1:11">
+      <c r="B9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" spans="1:11">
+      <c r="B10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="B11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" t="s">
+        <v>52</v>
+      </c>
+      <c r="H11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="B12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12" t="s">
+        <v>52</v>
+      </c>
+      <c r="H12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="B13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" t="s">
+        <v>52</v>
+      </c>
+      <c r="H13" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="B14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" t="s">
+        <v>52</v>
+      </c>
+      <c r="H14" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="B16" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" t="s">
+        <v>69</v>
+      </c>
+      <c r="D16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" t="s">
+        <v>70</v>
+      </c>
+      <c r="H16" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8">
+      <c r="B17" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" t="s">
+        <v>72</v>
+      </c>
+      <c r="D17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" t="s">
+        <v>73</v>
+      </c>
+      <c r="H17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>DTGridItemConfig</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>DRGridItemConfig</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Product/GridItemConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>c,s,e</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>DTGridManualRecipeConfig</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>DRGridManualRecipeConfig</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Product/GridManualRecipeConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>c,s,e</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E15" ns1:id="rId1" display="OneConfig.xlsx"/>
+    <hyperlink ref="E7" ns1:id="rId2" display="Game/Sound@Sound.xlsx" tooltip="mailto:Sound@Sound.xlsx"/>
+    <hyperlink ref="E8" ns1:id="rId3" display="Game/UISound@Sound.xlsx"/>
+    <hyperlink ref="E9" ns1:id="rId1" display="Game/Music@Sound.xlsx"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/Design/Excel/ET/Datas/__tables__.xlsx
+++ b/Design/Excel/ET/Datas/__tables__.xlsx
@@ -1252,7 +1252,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr/>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="29.1083333333333" customWidth="1"/>
@@ -1658,6 +1658,345 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>DTGridAutoRecipeConfig</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>DRGridAutoRecipeConfig</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Product/GridAutoRecipeConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>c,s,e</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>DTLevelConfig</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>DRLevelConfig</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Product/LevelConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>c,s,e</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>DTStationConfig</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>DRStationConfig</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Product/StationConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>c,s,e</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>DTInitialLayoutConfig</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>DRInitialLayoutConfig</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Product/InitialLayoutConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>c,s,e</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>DTDishConfig</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>DRDishConfig</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Product/DishConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>c,s,e</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>DTGridBakeRecipeConfig</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>DRGridBakeRecipeConfig</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Product/GridBakeRecipeConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>c,s,e</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>DTDishStageConfig</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>DRDishStageConfig</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Product/DishStageConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>c,s,e</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>DTCompanionConfig</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>DRCompanionConfig</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Product/CompanionConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>c,s,e</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>DTOrderConfig</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>DROrderConfig</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Product/OrderConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>c,s,e</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>DTTableConfig</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>DRTableConfig</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Product/TableConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>c,s,e</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>DTCustomerFlowConfig</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>DRCustomerFlowConfig</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Product/CustomerFlowConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>c,s,e</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>DTBuffConfig</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>DRBuffConfig</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Product/BuffConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>c,s,e</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E15" ns1:id="rId1" display="OneConfig.xlsx"/>

--- a/Design/Excel/ET/Datas/__tables__.xlsx
+++ b/Design/Excel/ET/Datas/__tables__.xlsx
@@ -1252,7 +1252,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr/>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="29.1083333333333" customWidth="1"/>
@@ -1997,6 +1997,116 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>DTSupplyConfig</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>DRSupplyConfig</t>
+        </is>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Product/SupplyConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>c,s,e</t>
+        </is>
+      </c>
+      <c r="I32" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J32" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K32" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>DTRenovationConfig</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>DRRenovationConfig</t>
+        </is>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Product/RenovationConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>c,s,e</t>
+        </is>
+      </c>
+      <c r="I33" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J33" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K33" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E15" ns1:id="rId1" display="OneConfig.xlsx"/>

--- a/Design/Excel/ET/Datas/__tables__.xlsx
+++ b/Design/Excel/ET/Datas/__tables__.xlsx
@@ -1252,7 +1252,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr/>
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="29.1083333333333" customWidth="1"/>
@@ -2107,6 +2107,48 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>DTStationUpgradeConfig</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>DRStationUpgradeConfig</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Product/StationUpgradeConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>c,s,e</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E15" ns1:id="rId1" display="OneConfig.xlsx"/>
